--- a/StructureDefinition-CertICAO.xlsx
+++ b/StructureDefinition-CertICAO.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-07T06:07:49+00:00</t>
+    <t>2023-11-14T21:40:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-CertICAO.xlsx
+++ b/StructureDefinition-CertICAO.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T21:40:28+00:00</t>
+    <t>2023-12-14T13:07:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-CertICAO.xlsx
+++ b/StructureDefinition-CertICAO.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-14T13:07:01+00:00</t>
+    <t>2023-12-14T13:50:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-CertICAO.xlsx
+++ b/StructureDefinition-CertICAO.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-14T13:50:56+00:00</t>
+    <t>2023-12-15T03:05:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-CertICAO.xlsx
+++ b/StructureDefinition-CertICAO.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T03:05:37+00:00</t>
+    <t>2024-01-19T16:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-CertICAO.xlsx
+++ b/StructureDefinition-CertICAO.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2625" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2545" uniqueCount="205">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T16:18:21+00:00</t>
+    <t>2024-04-24T00:11:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -175,9 +175,6 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>CertICAOVDS.data.extension</t>
   </si>
   <si>
@@ -236,9 +233,6 @@
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>CertICAOVDS.data.hdr</t>
@@ -958,7 +952,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK80"/>
+  <dimension ref="A1:AJ80"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.30078125" customWidth="true" bestFit="true"/>
@@ -995,7 +989,6 @@
     <col min="3" max="3" hidden="true" width="8.0" customWidth="false"/>
     <col min="17" max="17" width="20.703125" customWidth="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="4.2890625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1097,9 +1090,6 @@
       <c r="AJ1" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="AK1" t="s" s="2">
-        <v>37</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
@@ -1200,9 +1190,6 @@
       <c r="AJ2" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="AK2" t="s" s="2">
-        <v>37</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
@@ -1303,20 +1290,17 @@
       <c r="AJ3" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="AK3" t="s" s="2">
-        <v>52</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
@@ -1335,16 +1319,16 @@
         <v>37</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="M4" t="s" s="2">
+      <c r="N4" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="N4" t="s" s="2">
-        <v>58</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
@@ -1382,19 +1366,19 @@
         <v>37</v>
       </c>
       <c r="AB4" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AC4" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="AC4" t="s" s="2">
+      <c r="AD4" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE4" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="AD4" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE4" t="s" s="2">
+      <c r="AF4" t="s" s="2">
         <v>61</v>
-      </c>
-      <c r="AF4" t="s" s="2">
-        <v>62</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>38</v>
@@ -1406,22 +1390,19 @@
         <v>37</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AK4" t="s" s="2">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
@@ -1434,25 +1415,25 @@
         <v>37</v>
       </c>
       <c r="I5" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="J5" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="K5" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="J5" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="K5" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="O5" t="s" s="2">
         <v>68</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="O5" t="s" s="2">
-        <v>69</v>
       </c>
       <c r="P5" t="s" s="2">
         <v>37</v>
@@ -1501,7 +1482,7 @@
         <v>37</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>38</v>
@@ -1513,18 +1494,15 @@
         <v>37</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AK5" t="s" s="2">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1550,10 +1528,10 @@
         <v>44</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1604,7 +1582,7 @@
         <v>37</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>43</v>
@@ -1618,16 +1596,13 @@
       <c r="AJ6" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="AK6" t="s" s="2">
-        <v>37</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1721,20 +1696,17 @@
       <c r="AJ7" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="AK7" t="s" s="2">
-        <v>52</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -1753,16 +1725,16 @@
         <v>37</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>58</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1800,19 +1772,19 @@
         <v>37</v>
       </c>
       <c r="AB8" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AC8" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="AC8" t="s" s="2">
+      <c r="AD8" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE8" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="AD8" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE8" t="s" s="2">
+      <c r="AF8" t="s" s="2">
         <v>61</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>62</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>38</v>
@@ -1824,22 +1796,19 @@
         <v>37</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -1852,25 +1821,25 @@
         <v>37</v>
       </c>
       <c r="I9" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="K9" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="J9" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="K9" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="O9" t="s" s="2">
         <v>68</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="O9" t="s" s="2">
-        <v>69</v>
       </c>
       <c r="P9" t="s" s="2">
         <v>37</v>
@@ -1919,7 +1888,7 @@
         <v>37</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>38</v>
@@ -1931,18 +1900,15 @@
         <v>37</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AK9" t="s" s="2">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1968,10 +1934,10 @@
         <v>48</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2022,7 +1988,7 @@
         <v>37</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>43</v>
@@ -2034,18 +2000,15 @@
         <v>37</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK10" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2068,7 +2031,7 @@
         <v>37</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>4</v>
@@ -2125,7 +2088,7 @@
         <v>37</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>43</v>
@@ -2137,18 +2100,15 @@
         <v>37</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK11" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2174,10 +2134,10 @@
         <v>48</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2204,11 +2164,11 @@
         <v>37</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>37</v>
@@ -2226,7 +2186,7 @@
         <v>37</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>43</v>
@@ -2238,18 +2198,15 @@
         <v>37</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK12" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2275,10 +2232,10 @@
         <v>44</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2329,7 +2286,7 @@
         <v>37</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>43</v>
@@ -2343,16 +2300,13 @@
       <c r="AJ13" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="AK13" t="s" s="2">
-        <v>37</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2446,20 +2400,17 @@
       <c r="AJ14" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="AK14" t="s" s="2">
-        <v>52</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -2478,16 +2429,16 @@
         <v>37</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>58</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2525,19 +2476,19 @@
         <v>37</v>
       </c>
       <c r="AB15" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AC15" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="AC15" t="s" s="2">
+      <c r="AD15" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE15" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="AD15" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE15" t="s" s="2">
+      <c r="AF15" t="s" s="2">
         <v>61</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>62</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>38</v>
@@ -2549,22 +2500,19 @@
         <v>37</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AK15" t="s" s="2">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -2577,25 +2525,25 @@
         <v>37</v>
       </c>
       <c r="I16" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="J16" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="K16" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="J16" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="K16" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="O16" t="s" s="2">
         <v>68</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>69</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>37</v>
@@ -2644,7 +2592,7 @@
         <v>37</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>38</v>
@@ -2656,18 +2604,15 @@
         <v>37</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AK16" t="s" s="2">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2693,13 +2638,13 @@
         <v>44</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2749,7 +2694,7 @@
         <v>37</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>43</v>
@@ -2763,16 +2708,13 @@
       <c r="AJ17" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="AK17" t="s" s="2">
-        <v>37</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2866,20 +2808,17 @@
       <c r="AJ18" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="AK18" t="s" s="2">
-        <v>52</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -2898,16 +2837,16 @@
         <v>37</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>58</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -2945,19 +2884,19 @@
         <v>37</v>
       </c>
       <c r="AB19" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AC19" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="AC19" t="s" s="2">
+      <c r="AD19" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE19" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="AD19" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE19" t="s" s="2">
+      <c r="AF19" t="s" s="2">
         <v>61</v>
-      </c>
-      <c r="AF19" t="s" s="2">
-        <v>62</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>38</v>
@@ -2969,22 +2908,19 @@
         <v>37</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AK19" t="s" s="2">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -2997,25 +2933,25 @@
         <v>37</v>
       </c>
       <c r="I20" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="J20" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="K20" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="O20" t="s" s="2">
         <v>68</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>69</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>37</v>
@@ -3064,7 +3000,7 @@
         <v>37</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>38</v>
@@ -3076,18 +3012,15 @@
         <v>37</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3113,10 +3046,10 @@
         <v>48</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3167,7 +3100,7 @@
         <v>37</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>43</v>
@@ -3179,18 +3112,15 @@
         <v>37</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK21" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3213,13 +3143,13 @@
         <v>37</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3270,7 +3200,7 @@
         <v>37</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>38</v>
@@ -3282,18 +3212,15 @@
         <v>37</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK22" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3319,10 +3246,10 @@
         <v>48</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3373,7 +3300,7 @@
         <v>37</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>38</v>
@@ -3385,18 +3312,15 @@
         <v>37</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK23" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3422,10 +3346,10 @@
         <v>48</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3476,7 +3400,7 @@
         <v>37</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>43</v>
@@ -3488,18 +3412,15 @@
         <v>37</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK24" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3525,10 +3446,10 @@
         <v>48</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3579,7 +3500,7 @@
         <v>37</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>38</v>
@@ -3591,18 +3512,15 @@
         <v>37</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK25" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3628,10 +3546,10 @@
         <v>48</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3682,7 +3600,7 @@
         <v>37</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>38</v>
@@ -3694,18 +3612,15 @@
         <v>37</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK26" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3731,10 +3646,10 @@
         <v>48</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3785,7 +3700,7 @@
         <v>37</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>38</v>
@@ -3797,18 +3712,15 @@
         <v>37</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK27" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3834,10 +3746,10 @@
         <v>48</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3888,7 +3800,7 @@
         <v>37</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>38</v>
@@ -3900,18 +3812,15 @@
         <v>37</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK28" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3937,10 +3846,10 @@
         <v>44</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3991,7 +3900,7 @@
         <v>37</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>38</v>
@@ -4005,16 +3914,13 @@
       <c r="AJ29" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="AK29" t="s" s="2">
-        <v>37</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4108,20 +4014,17 @@
       <c r="AJ30" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="AK30" t="s" s="2">
-        <v>52</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4140,16 +4043,16 @@
         <v>37</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>58</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4187,19 +4090,19 @@
         <v>37</v>
       </c>
       <c r="AB31" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AC31" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="AC31" t="s" s="2">
+      <c r="AD31" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE31" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="AD31" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE31" t="s" s="2">
+      <c r="AF31" t="s" s="2">
         <v>61</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>62</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>38</v>
@@ -4211,22 +4114,19 @@
         <v>37</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AK31" t="s" s="2">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4239,25 +4139,25 @@
         <v>37</v>
       </c>
       <c r="I32" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="J32" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="K32" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="O32" t="s" s="2">
         <v>68</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>69</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>37</v>
@@ -4306,7 +4206,7 @@
         <v>37</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>38</v>
@@ -4318,18 +4218,15 @@
         <v>37</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4355,10 +4252,10 @@
         <v>48</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4409,7 +4306,7 @@
         <v>37</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>43</v>
@@ -4421,18 +4318,15 @@
         <v>37</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK33" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4458,10 +4352,10 @@
         <v>48</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4512,7 +4406,7 @@
         <v>37</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>43</v>
@@ -4524,18 +4418,15 @@
         <v>37</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK34" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4561,10 +4452,10 @@
         <v>44</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4615,7 +4506,7 @@
         <v>37</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>43</v>
@@ -4629,16 +4520,13 @@
       <c r="AJ35" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="AK35" t="s" s="2">
-        <v>37</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4732,20 +4620,17 @@
       <c r="AJ36" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="AK36" t="s" s="2">
-        <v>52</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -4764,16 +4649,16 @@
         <v>37</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>58</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -4811,19 +4696,19 @@
         <v>37</v>
       </c>
       <c r="AB37" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AC37" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="AC37" t="s" s="2">
+      <c r="AD37" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE37" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="AD37" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE37" t="s" s="2">
+      <c r="AF37" t="s" s="2">
         <v>61</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>62</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>38</v>
@@ -4835,22 +4720,19 @@
         <v>37</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -4863,25 +4745,25 @@
         <v>37</v>
       </c>
       <c r="I38" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="J38" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="K38" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="O38" t="s" s="2">
         <v>68</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>69</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>37</v>
@@ -4930,7 +4812,7 @@
         <v>37</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>38</v>
@@ -4942,18 +4824,15 @@
         <v>37</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AK38" t="s" s="2">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4979,10 +4858,10 @@
         <v>48</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5033,7 +4912,7 @@
         <v>37</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>43</v>
@@ -5045,18 +4924,15 @@
         <v>37</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK39" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5082,10 +4958,10 @@
         <v>48</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5136,7 +5012,7 @@
         <v>37</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>43</v>
@@ -5148,18 +5024,15 @@
         <v>37</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK40" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5185,10 +5058,10 @@
         <v>48</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5239,7 +5112,7 @@
         <v>37</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>43</v>
@@ -5251,18 +5124,15 @@
         <v>37</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK41" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5288,10 +5158,10 @@
         <v>44</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5342,7 +5212,7 @@
         <v>37</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>38</v>
@@ -5356,16 +5226,13 @@
       <c r="AJ42" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="AK42" t="s" s="2">
-        <v>37</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5459,20 +5326,17 @@
       <c r="AJ43" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="AK43" t="s" s="2">
-        <v>52</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -5491,16 +5355,16 @@
         <v>37</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>58</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -5538,19 +5402,19 @@
         <v>37</v>
       </c>
       <c r="AB44" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AC44" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="AC44" t="s" s="2">
+      <c r="AD44" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE44" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="AD44" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE44" t="s" s="2">
+      <c r="AF44" t="s" s="2">
         <v>61</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>62</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>38</v>
@@ -5562,22 +5426,19 @@
         <v>37</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -5590,25 +5451,25 @@
         <v>37</v>
       </c>
       <c r="I45" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="J45" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="O45" t="s" s="2">
         <v>68</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>69</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>37</v>
@@ -5657,7 +5518,7 @@
         <v>37</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>38</v>
@@ -5669,18 +5530,15 @@
         <v>37</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5703,13 +5561,13 @@
         <v>37</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -5760,7 +5618,7 @@
         <v>37</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>43</v>
@@ -5772,18 +5630,15 @@
         <v>37</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK46" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5806,13 +5661,13 @@
         <v>37</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -5863,7 +5718,7 @@
         <v>37</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>43</v>
@@ -5875,18 +5730,15 @@
         <v>37</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK47" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5912,10 +5764,10 @@
         <v>44</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -5966,7 +5818,7 @@
         <v>37</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>38</v>
@@ -5980,16 +5832,13 @@
       <c r="AJ48" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="AK48" t="s" s="2">
-        <v>37</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6083,20 +5932,17 @@
       <c r="AJ49" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="AK49" t="s" s="2">
-        <v>52</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -6115,16 +5961,16 @@
         <v>37</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>58</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -6162,19 +6008,19 @@
         <v>37</v>
       </c>
       <c r="AB50" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AC50" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="AC50" t="s" s="2">
+      <c r="AD50" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE50" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="AD50" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE50" t="s" s="2">
+      <c r="AF50" t="s" s="2">
         <v>61</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>62</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>38</v>
@@ -6186,22 +6032,19 @@
         <v>37</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -6214,25 +6057,25 @@
         <v>37</v>
       </c>
       <c r="I51" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="J51" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="O51" t="s" s="2">
         <v>68</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>69</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>37</v>
@@ -6281,7 +6124,7 @@
         <v>37</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>38</v>
@@ -6293,18 +6136,15 @@
         <v>37</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6330,10 +6170,10 @@
         <v>48</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6360,11 +6200,11 @@
         <v>37</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>37</v>
@@ -6382,7 +6222,7 @@
         <v>37</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>43</v>
@@ -6394,18 +6234,15 @@
         <v>37</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK52" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6431,10 +6268,10 @@
         <v>48</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6461,11 +6298,11 @@
         <v>37</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>37</v>
@@ -6483,7 +6320,7 @@
         <v>37</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>43</v>
@@ -6495,18 +6332,15 @@
         <v>37</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK53" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -6532,10 +6366,10 @@
         <v>48</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6562,11 +6396,11 @@
         <v>37</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>37</v>
@@ -6584,7 +6418,7 @@
         <v>37</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>38</v>
@@ -6596,18 +6430,15 @@
         <v>37</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK54" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6633,10 +6464,10 @@
         <v>48</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6687,7 +6518,7 @@
         <v>37</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>38</v>
@@ -6699,18 +6530,15 @@
         <v>37</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK55" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -6736,10 +6564,10 @@
         <v>48</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -6790,7 +6618,7 @@
         <v>37</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>38</v>
@@ -6802,18 +6630,15 @@
         <v>37</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK56" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -6839,10 +6664,10 @@
         <v>44</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -6893,7 +6718,7 @@
         <v>37</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>38</v>
@@ -6907,16 +6732,13 @@
       <c r="AJ57" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="AK57" t="s" s="2">
-        <v>37</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7010,20 +6832,17 @@
       <c r="AJ58" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="AK58" t="s" s="2">
-        <v>52</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -7042,16 +6861,16 @@
         <v>37</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="M59" t="s" s="2">
+      <c r="N59" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>58</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -7089,19 +6908,19 @@
         <v>37</v>
       </c>
       <c r="AB59" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AC59" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="AC59" t="s" s="2">
+      <c r="AD59" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE59" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="AD59" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE59" t="s" s="2">
+      <c r="AF59" t="s" s="2">
         <v>61</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>62</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>38</v>
@@ -7113,22 +6932,19 @@
         <v>37</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -7141,25 +6957,25 @@
         <v>37</v>
       </c>
       <c r="I60" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="J60" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="N60" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="O60" t="s" s="2">
         <v>68</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>69</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>37</v>
@@ -7208,7 +7024,7 @@
         <v>37</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>38</v>
@@ -7220,18 +7036,15 @@
         <v>37</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7257,10 +7070,10 @@
         <v>48</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7287,11 +7100,11 @@
         <v>37</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Y61" s="2"/>
       <c r="Z61" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>37</v>
@@ -7309,7 +7122,7 @@
         <v>37</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>43</v>
@@ -7321,18 +7134,15 @@
         <v>37</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK61" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7358,10 +7168,10 @@
         <v>48</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -7412,7 +7222,7 @@
         <v>37</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>43</v>
@@ -7424,18 +7234,15 @@
         <v>37</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK62" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7461,10 +7268,10 @@
         <v>48</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7515,7 +7322,7 @@
         <v>37</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>38</v>
@@ -7527,18 +7334,15 @@
         <v>37</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK63" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7564,10 +7368,10 @@
         <v>44</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7618,7 +7422,7 @@
         <v>37</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>43</v>
@@ -7632,16 +7436,13 @@
       <c r="AJ64" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="AK64" t="s" s="2">
-        <v>37</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -7735,20 +7536,17 @@
       <c r="AJ65" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="AK65" t="s" s="2">
-        <v>52</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -7767,16 +7565,16 @@
         <v>37</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="L66" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="L66" t="s" s="2">
+      <c r="M66" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="M66" t="s" s="2">
+      <c r="N66" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>58</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -7814,19 +7612,19 @@
         <v>37</v>
       </c>
       <c r="AB66" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AC66" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="AC66" t="s" s="2">
+      <c r="AD66" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE66" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="AD66" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE66" t="s" s="2">
+      <c r="AF66" t="s" s="2">
         <v>61</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>62</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>38</v>
@@ -7838,22 +7636,19 @@
         <v>37</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -7866,25 +7661,25 @@
         <v>37</v>
       </c>
       <c r="I67" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="L67" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="J67" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="L67" t="s" s="2">
+      <c r="M67" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="O67" t="s" s="2">
         <v>68</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>69</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>37</v>
@@ -7933,7 +7728,7 @@
         <v>37</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>38</v>
@@ -7945,18 +7740,15 @@
         <v>37</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -7979,13 +7771,13 @@
         <v>37</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8036,7 +7828,7 @@
         <v>37</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>43</v>
@@ -8048,18 +7840,15 @@
         <v>37</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK68" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8082,13 +7871,13 @@
         <v>37</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -8139,7 +7928,7 @@
         <v>37</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>43</v>
@@ -8151,18 +7940,15 @@
         <v>37</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK69" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8188,10 +7974,10 @@
         <v>48</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8218,11 +8004,11 @@
         <v>37</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>37</v>
@@ -8240,7 +8026,7 @@
         <v>37</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>43</v>
@@ -8252,18 +8038,15 @@
         <v>37</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK70" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8289,10 +8072,10 @@
         <v>48</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8343,7 +8126,7 @@
         <v>37</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>43</v>
@@ -8355,18 +8138,15 @@
         <v>37</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK71" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8392,10 +8172,10 @@
         <v>48</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8446,7 +8226,7 @@
         <v>37</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>43</v>
@@ -8458,18 +8238,15 @@
         <v>37</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK72" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8492,13 +8269,13 @@
         <v>37</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -8549,7 +8326,7 @@
         <v>37</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>38</v>
@@ -8561,18 +8338,15 @@
         <v>37</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK73" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -8598,10 +8372,10 @@
         <v>44</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -8652,7 +8426,7 @@
         <v>37</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>38</v>
@@ -8666,16 +8440,13 @@
       <c r="AJ74" t="s" s="2">
         <v>46</v>
       </c>
-      <c r="AK74" t="s" s="2">
-        <v>37</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -8769,20 +8540,17 @@
       <c r="AJ75" t="s" s="2">
         <v>37</v>
       </c>
-      <c r="AK75" t="s" s="2">
-        <v>52</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -8801,16 +8569,16 @@
         <v>37</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>55</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>56</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>58</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -8848,19 +8616,19 @@
         <v>37</v>
       </c>
       <c r="AB76" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="AC76" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="AC76" t="s" s="2">
+      <c r="AD76" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="AE76" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="AD76" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AE76" t="s" s="2">
+      <c r="AF76" t="s" s="2">
         <v>61</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>62</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>38</v>
@@ -8872,22 +8640,19 @@
         <v>37</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -8900,25 +8665,25 @@
         <v>37</v>
       </c>
       <c r="I77" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="L77" t="s" s="2">
         <v>66</v>
       </c>
-      <c r="J77" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="L77" t="s" s="2">
+      <c r="M77" t="s" s="2">
         <v>67</v>
       </c>
-      <c r="M77" t="s" s="2">
+      <c r="N77" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="O77" t="s" s="2">
         <v>68</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>69</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>37</v>
@@ -8967,7 +8732,7 @@
         <v>37</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>38</v>
@@ -8979,18 +8744,15 @@
         <v>37</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9016,10 +8778,10 @@
         <v>48</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9070,7 +8832,7 @@
         <v>37</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>43</v>
@@ -9082,18 +8844,15 @@
         <v>37</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK78" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9119,10 +8878,10 @@
         <v>48</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -9173,7 +8932,7 @@
         <v>37</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>43</v>
@@ -9185,18 +8944,15 @@
         <v>37</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK79" t="s" s="2">
         <v>37</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9222,10 +8978,10 @@
         <v>48</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9276,7 +9032,7 @@
         <v>37</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>43</v>
@@ -9288,9 +9044,6 @@
         <v>37</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="AK80" t="s" s="2">
         <v>37</v>
       </c>
     </row>

--- a/StructureDefinition-CertICAO.xlsx
+++ b/StructureDefinition-CertICAO.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-30T07:55:09+00:00</t>
+    <t>2024-07-30T11:13:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
